--- a/out/Attention-Mamba1_repeat_5_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>2.037571854792519</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>-5.601964558998588e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0.02412043292155979</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0.04830523690135265</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0.09318916116828496</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>2.637571854792519</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0.2106264648099237</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0.02866550836693979</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.5384768609581863</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0.1746497130737535</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0.005815296308964131</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0.1575704956406969</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0.005035223133389709</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0.1618200877040143</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0.002459062401495688</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0.1616977908752719</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0.001170982035548672</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0.1615780932957016</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0.00048490497867579</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0.161375571088064</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0.0003345354556114936</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0.1615592934364739</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0.000136743145206162</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0.1614978751733804</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>6.849887722179201e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0.1614979820601272</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>2.386752475476279e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0.1614771317449561</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>1.0461098056069e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0.1614747274965521</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>2.905404250635916e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0.1614694864422635</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>-1.270220690815108e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0.1614640313969806</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0.1614585257631533</v>
       </c>
     </row>
     <row r="60">
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0.1614533322684192</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0.1614480044740965</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1614480443295687</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0.161448084185041</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.1614480762139466</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0.1614482356358357</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0.1614484907108585</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1614482436069301</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.1614482037514579</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1614482117225523</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1614482436069301</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0.1614483392600638</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0.161448275491308</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0.1614482356358357</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1614482117225523</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0.1614479646186242</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0.1614478849076794</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0.1614479327342461</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.1614480523006632</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.1614480363584743</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0.1614480523006632</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0.1614480363584743</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1614480921561355</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1614480921561355</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1614480921561355</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0.1614482436069301</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0.1614484588264807</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.1614483711444417</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.1614483233178749</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0.1614483711444417</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0.161448187809269</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0.1614481957803634</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0.1614482037514579</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1614482117225523</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0.1614482117225523</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0.1614482515780246</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0.1614483153467805</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0.1614484269421028</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0.1614484747686696</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0.1614484349131973</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0.1614483631733472</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0.161448482739764</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0.1614483233178749</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0.1614480921561355</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1614480443295687</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0.1614480762139466</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0.1614480602717576</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0.1614479407053406</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0.1614479008498683</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1614480443295687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0.1614481798381745</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0.1614481638959856</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0.1614481001272299</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.161447996503002</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0.1614478769365849</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0.161447996503002</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0.1614480443295687</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0.1614481399827022</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0.1614480204162854</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-1.138476860958186</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0.1614480283873798</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>-7.549743061384651e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03250700163653785</v>
+        <v>0</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.06510075586587261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1255909113784595</v>
+        <v>0</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.2838603620831945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.03863297737825833</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2353747611161221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.00783871192263551</v>
+        <v>0</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2123591837899089</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.006787130236714228</v>
+        <v>0</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2180879121040965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.003315884100197597</v>
+        <v>0</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.217924827968996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001579903061546279</v>
+        <v>0</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2177652469128931</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0006552583008062353</v>
+        <v>0</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2174940408466905</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0004526011935854903</v>
+        <v>0</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.217743387102616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0001857089590046543</v>
+        <v>0</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2176623513565788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>9.388939844386562e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2176642463538488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>3.383994239731721e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2176377769955543</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.618743066942789e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.2176363164230874</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>5.728762911577315e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2176309892779815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-2.045694596194254e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2176253723353827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.694140733653212e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2176196491787541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.173194643232597e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2176144078574532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2176091199186027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.817481666896968e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2176038480845517</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51022,17 +51022,17 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2176039277954963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2176043343213138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2176041828705191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2176041191017632</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.217604079246291</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2176038082290795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2176037285181347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2176037763447014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2176038959111185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2176038799689296</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2176040872173854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.217604302436936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2176042147548969</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2176040314197242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2176040393908187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2176040473619131</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2176040553330076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2176040951884799</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2176041589572358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2176042705525581</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2176043183791249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2176042785236526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2176042067838025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2176043263502193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2176041669283302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2176039357665908</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2176039198244019</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2176039038822129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2176037843157959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2176037444603236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2176040234486298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2176040075064408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2176039437376852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2176037205470402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2176038401134573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.217603887940024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2176039835931575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2176038640267406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.79359707945414e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3</v>
+        <v>-0.04000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2176038719978351</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.006645508110523224</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.009573385119438171</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.007372155785560608</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.006175614893436432</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.007131472229957581</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.009694464504718781</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.00661073625087738</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.006164662539958954</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.007524453103542328</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.005620472133159637</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.006534986197948456</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.00601533055305481</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.007698051631450653</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01034983247518539</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01185150444507599</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01212372630834579</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.009338937699794769</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.009596414864063263</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.009505718946456909</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.007841691374778748</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.007443077862262726</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.008337676525115967</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.00932919979095459</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.01048678159713745</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008828707039356232</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.008454427123069763</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008119456470012665</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.007197462022304535</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.008254610002040863</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01137121766805649</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.008330367505550385</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.008718766272068024</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.007488109171390533</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.006762512028217316</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.006519220769405365</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.007286079227924347</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.008055798709392548</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.008640535175800323</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01266155391931534</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01499810069799423</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.02149252220988274</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,17 +35122,17 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.02408332750201225</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>0</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,21 +35913,21 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0368429571390152</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.03496107459068298</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01283718645572662</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01723473891615868</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,21 +39093,21 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01101819425821304</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01477239280939102</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01240541040897369</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01250024884939194</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01063650101423264</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01566099375486374</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,21 +43863,21 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.01553360000252724</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,21 +44658,21 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01060774177312851</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,21 +45453,21 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0104973316192627</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,21 +46248,21 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.007947206497192383</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,21 +47043,21 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.008604347705841064</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,21 +47838,21 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00886758416891098</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.008924379944801331</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.009921029210090637</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.009442940354347229</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01097172498703003</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51817,17 +51817,17 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.008920453488826752</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52612,17 +52612,17 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01147209107875824</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53407,17 +53407,17 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.009912252426147461</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54202,17 +54202,17 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01444182544946671</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -54997,17 +54997,17 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01136673986911774</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55792,17 +55792,17 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.009833253920078278</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56587,17 +56587,17 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.0109720453619957</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57382,17 +57382,17 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.008834749460220337</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58177,17 +58177,17 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.008697882294654846</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58972,17 +58972,17 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.008580774068832397</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59767,17 +59767,17 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0244477391242981</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60562,17 +60562,17 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.01279498264193535</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61357,17 +61357,17 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.009109683334827423</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62152,17 +62152,17 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.007880993187427521</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62947,17 +62947,17 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.0100889578461647</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63742,17 +63742,17 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.008780337870121002</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64537,17 +64537,17 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00766272097826004</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.007951132953166962</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.007075563073158264</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.008259378373622894</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.008065268397331238</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.008613236248493195</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.008177809417247772</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.006866477429866791</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01160409301519394</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71692,17 +71692,17 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.008079633116722107</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01349004358053207</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>0</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73282,17 +73282,17 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.008151374757289886</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.008018702268600464</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.008914865553379059</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75667,17 +75667,17 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.007496483623981476</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.007122606039047241</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77257,17 +77257,17 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.008319549262523651</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.006893597543239594</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.006826572120189667</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
-        <v>0</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79642,17 +79642,17 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01097191870212555</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80437,17 +80437,17 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.00965108722448349</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.009954355657100677</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.007976189255714417</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.008891798555850983</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.009528473019599915</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.009348049759864807</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>0</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01061664521694183</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.008614271879196167</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.008436538279056549</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.00738178938627243</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.008223205804824829</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.007055662572383881</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007008381187915802</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.007594332098960876</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.007626920938491821</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.00828561931848526</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.007757164537906647</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.006675891578197479</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.007279172539710999</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.007458776235580444</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.008893579244613647</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC120" t="n">
-        <v>0</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01048406958580017</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.007980197668075562</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.008843608200550079</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.007421225309371948</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.007776305079460144</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.04000000000000001</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>0</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.79359707945414e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.009775139391422272</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.04000000000000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000001.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.006645508110523224</v>
+        <v>0.00664549320936203</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.007372155785560608</v>
+        <v>0.007372140884399414</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.006175614893436432</v>
+        <v>0.006175622344017029</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.8599999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.007131472229957581</v>
+        <v>0.007131464779376984</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.009694464504718781</v>
+        <v>0.009694457054138184</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.00661073625087738</v>
+        <v>0.006610728800296783</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.8599999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.006164662539958954</v>
+        <v>0.00616464763879776</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.8599999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.007524453103542328</v>
+        <v>0.007524460554122925</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.005620472133159637</v>
+        <v>0.005620487034320831</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.00601533055305481</v>
+        <v>0.006015323102474213</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.01034983247518539</v>
+        <v>0.01034983992576599</v>
       </c>
       <c r="JB15" t="n">
         <v>0.4399999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.01185150444507599</v>
+        <v>0.01185151934623718</v>
       </c>
       <c r="JB16" t="n">
         <v>0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.01212372630834579</v>
+        <v>0.01212373375892639</v>
       </c>
       <c r="JB17" t="n">
         <v>0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.009596414864063263</v>
+        <v>0.00959642231464386</v>
       </c>
       <c r="JB19" t="n">
         <v>0.5799999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.009505718946456909</v>
+        <v>0.009505733847618103</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.007841691374778748</v>
+        <v>0.007841713726520538</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.007443077862262726</v>
+        <v>0.00744309276342392</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.008337676525115967</v>
+        <v>0.00833766907453537</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.00932919979095459</v>
+        <v>0.009329184889793396</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.01048678159713745</v>
+        <v>0.01048678904771805</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.02000000000000007</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.008454427123069763</v>
+        <v>0.008454442024230957</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.008254610002040863</v>
+        <v>0.00825461745262146</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.01137121766805649</v>
+        <v>0.01137124747037888</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.008330367505550385</v>
+        <v>0.008330360054969788</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.008718766272068024</v>
+        <v>0.00871875137090683</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.006762512028217316</v>
+        <v>0.006762489676475525</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.006519220769405365</v>
+        <v>0.006519243121147156</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.007286079227924347</v>
+        <v>0.007286094129085541</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.008055798709392548</v>
+        <v>0.008055813610553741</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.008640535175800323</v>
+        <v>0.008640512824058533</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01266155391931534</v>
+        <v>0.01266153901815414</v>
       </c>
       <c r="JB40" t="n">
         <v>0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.01499810069799423</v>
+        <v>0.01499807834625244</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.02149252220988274</v>
+        <v>0.02149252593517303</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.02408332750201225</v>
+        <v>0.02408332377672195</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.03496107459068298</v>
+        <v>0.03496106341481209</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01283718645572662</v>
+        <v>0.01283720135688782</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0.5664011813620098</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01723473891615868</v>
+        <v>0.01723473519086838</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
         <v>0.5110173888417329</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01101819425821304</v>
+        <v>0.01101820915937424</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0.5248062758631562</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.01477239280939102</v>
+        <v>0.01477240025997162</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0.524420894243811</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01240541040897369</v>
+        <v>0.01240543276071548</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0.5240439424238605</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01566099375486374</v>
+        <v>0.01566100120544434</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.3</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.01553360000252724</v>
+        <v>0.01553361490368843</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC54" t="n">
         <v>0.5238290030499527</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.01060774177312851</v>
+        <v>0.0106077641248703</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.008604347705841064</v>
+        <v>0.008604377508163452</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.00886758416891098</v>
+        <v>0.008867569267749786</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.009921029210090637</v>
+        <v>0.009921044111251831</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.01097172498703003</v>
+        <v>0.01097174733877182</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.008920453488826752</v>
+        <v>0.008920468389987946</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01147209107875824</v>
+        <v>0.01147206127643585</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.1199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.01444182544946671</v>
+        <v>0.0144418403506279</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.1199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01136673986911774</v>
+        <v>0.01136675477027893</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.009833253920078278</v>
+        <v>0.009833231568336487</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.0109720453619957</v>
+        <v>0.01097205281257629</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.3999999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.008834749460220337</v>
+        <v>0.008834734559059143</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.008697882294654846</v>
+        <v>0.008697889745235443</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.008580774068832397</v>
+        <v>0.008580766618251801</v>
       </c>
       <c r="JB73" t="n">
         <v>0.16</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0244477391242981</v>
+        <v>0.02444775775074959</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.01279498264193535</v>
+        <v>0.01279497146606445</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1600000000000001</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.009109683334827423</v>
+        <v>0.00910969078540802</v>
       </c>
       <c r="JB76" t="n">
         <v>0.16</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.007880993187427521</v>
+        <v>0.00788097083568573</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.008780337870121002</v>
+        <v>0.008780330419540405</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.00766272097826004</v>
+        <v>0.007662706077098846</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.007951132953166962</v>
+        <v>0.007951155304908752</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.007075563073158264</v>
+        <v>0.007075577974319458</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.008259378373622894</v>
+        <v>0.008259393274784088</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.008065268397331238</v>
+        <v>0.008065275847911835</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.008613236248493195</v>
+        <v>0.008613251149654388</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.008177809417247772</v>
+        <v>0.008177801966667175</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.006866477429866791</v>
+        <v>0.006866484880447388</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.01160409301519394</v>
+        <v>0.01160410046577454</v>
       </c>
       <c r="JB88" t="n">
         <v>0.1600000000000001</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.008079633116722107</v>
+        <v>0.008079648017883301</v>
       </c>
       <c r="JB89" t="n">
         <v>0.16</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01349004358053207</v>
+        <v>0.01349005475640297</v>
       </c>
       <c r="JB90" t="n">
         <v>0.1600000000000001</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.008151374757289886</v>
+        <v>0.00815136730670929</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.1199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.008018702268600464</v>
+        <v>0.008018694818019867</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.1199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.008914865553379059</v>
+        <v>0.008914873003959656</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.007496483623981476</v>
+        <v>0.007496476173400879</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.007122606039047241</v>
+        <v>0.007122628390789032</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.008319549262523651</v>
+        <v>0.008319534361362457</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.006893597543239594</v>
+        <v>0.006893619894981384</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.01097191870212555</v>
+        <v>0.01097190380096436</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.00965108722448349</v>
+        <v>0.009651094675064087</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.009954355657100677</v>
+        <v>0.009954340755939484</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.008891798555850983</v>
+        <v>0.008891783654689789</v>
       </c>
       <c r="JB103" t="n">
         <v>0.16</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.009348049759864807</v>
+        <v>0.009348034858703613</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.008436538279056549</v>
+        <v>0.008436523377895355</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.00738178938627243</v>
+        <v>0.007381811738014221</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.008223205804824829</v>
+        <v>0.008223213255405426</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.007055662572383881</v>
+        <v>0.007055670022964478</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.007008381187915802</v>
+        <v>0.007008396089076996</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.007594332098960876</v>
+        <v>0.007594309747219086</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.007626920938491821</v>
+        <v>0.007626898586750031</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.00828561931848526</v>
+        <v>0.008285626769065857</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.006675891578197479</v>
+        <v>0.006675884127616882</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.007279172539710999</v>
+        <v>0.007279187440872192</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.007458776235580444</v>
+        <v>0.007458783686161041</v>
       </c>
       <c r="JB119" t="n">
         <v>0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.008893579244613647</v>
+        <v>0.008893571794033051</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1600000000000001</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.008843608200550079</v>
+        <v>0.008843593299388885</v>
       </c>
       <c r="JB123" t="n">
         <v>0.1600000000000001</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.007421225309371948</v>
+        <v>0.007421217858791351</v>
       </c>
       <c r="JB124" t="n">
         <v>0.02000000000000007</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.009775139391422272</v>
+        <v>0.009775131940841675</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.5799999999999998</v>
